--- a/resampling/input/accessibility_reports_generated/DRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/DRC_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q64" headerRowCount="1">
-  <autoFilter ref="A1:Q64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q106" headerRowCount="1">
+  <autoFilter ref="A1:Q106"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O69" headerRowCount="1">
-  <autoFilter ref="A1:O69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O53" headerRowCount="1">
+  <autoFilter ref="A1:O53"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 63 wards, 68 clusters</t>
+          <t>Assigned to you: 105 wards, 52 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -833,25 +833,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Illela</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Gada; Isa; Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>96</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -874,7 +882,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rungumawa Gatti</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -886,13 +894,13 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -915,25 +923,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Darna Sabon Gari</t>
+          <t>Rungumawa Gatti</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Gwadabawa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -964,25 +964,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tozai</t>
+          <t>Araba</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gada</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1005,25 +1013,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gidan Hamma</t>
+          <t>Asara</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1046,25 +1062,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kalmalo</t>
+          <t>Damba</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gwadabawa; Tangaza</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1087,17 +1111,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gidan Katta</t>
+          <t>Darna Sabon Gari</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1105,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1128,17 +1160,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kadadi</t>
+          <t>Darna Tsolawo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1146,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1175,11 +1215,19 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -1187,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1210,7 +1258,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Asara</t>
+          <t>Gidan Hamma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1221,7 +1269,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Gada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1230,13 +1278,13 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1259,7 +1307,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Araba</t>
+          <t>Gidan Katta</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1277,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1300,7 +1348,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mamman Suka</t>
+          <t>Gigane</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1311,7 +1359,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Gwadabawa; Tangaza</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1320,13 +1368,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1349,7 +1397,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salame</t>
+          <t>Kadadi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1360,7 +1408,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Gada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1375,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1398,19 +1446,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Darna Tsolawo</t>
+          <t>Kadassaka</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gada</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1434,30 +1490,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Isa North</t>
+          <t>Kalmalo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1475,30 +1539,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Isa South</t>
+          <t>Kiri</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gada; Goronyo; Gwadabawa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1516,30 +1588,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bargaja</t>
+          <t>Kyadawa Holai</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gada</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1557,30 +1637,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gebe A</t>
+          <t>Mamman Suka</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1598,12 +1686,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tidibale</t>
+          <t>Mammande</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1614,7 +1702,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goronyo</t>
+          <t>Gada; Goronyo; Gwadabawa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1623,13 +1711,13 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1647,30 +1735,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gebe B</t>
+          <t>Ruwa Wuri</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gudu; Tangaza</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1688,30 +1784,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turba</t>
+          <t>Salame</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1729,30 +1833,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tsabre</t>
+          <t>Salewa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gwadabawa; Tangaza</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1775,7 +1887,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yanfako</t>
+          <t>Bargaja</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1787,13 +1899,13 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1816,25 +1928,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Katuru</t>
+          <t>Faru Magami</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1852,12 +1972,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Magajin Gari B</t>
+          <t>Galadi</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1869,13 +1989,13 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1893,30 +2013,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gandu</t>
+          <t>Gandi 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Goronyo; Rabah</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1934,30 +2062,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Waziri A</t>
+          <t>Gangara</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1975,12 +2111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gidan Igwai</t>
+          <t>Gebe A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1992,13 +2128,13 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2016,38 +2152,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kalambaina</t>
+          <t>Gebe B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Wamako</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2065,12 +2193,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Magajin Rafi A</t>
+          <t>Isa North</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2082,13 +2210,13 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2106,12 +2234,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Magajin Gari A</t>
+          <t>Isa South</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2123,13 +2251,13 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2147,12 +2275,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Magajin Rafi B</t>
+          <t>Kalgo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2163,7 +2291,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sabon Birni</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2172,13 +2300,13 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2196,12 +2324,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Waziri B</t>
+          <t>Katuru</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2213,13 +2341,13 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2237,12 +2365,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Waziri C</t>
+          <t>Kaya</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2254,13 +2382,13 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2278,12 +2406,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sarkin Musulmi B</t>
+          <t>Mashema</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2295,13 +2423,13 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2319,12 +2447,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sarkin Addar A</t>
+          <t>Rimawa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2335,7 +2463,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Gada; Goronyo; Sabon Birni</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2344,7 +2472,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2368,12 +2496,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sarkin Addar B</t>
+          <t>Sabon Gari Dole</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2384,7 +2512,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Goronyo; Rabah; Wurno</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2393,7 +2521,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2417,12 +2545,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sarkin Musulmi A</t>
+          <t>Shanawa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2434,7 +2562,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2458,12 +2586,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gagi A</t>
+          <t>Tidibale</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2474,7 +2602,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dange-Shuni; Kware</t>
+          <t>Goronyo; Rabah; Sabon Birni</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2483,13 +2611,13 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2507,30 +2635,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tudun Wada A</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gada; Illela; Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2548,30 +2684,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gagi C</t>
+          <t>Tsabre</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2589,30 +2733,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gagi B</t>
+          <t>Turba</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2630,12 +2782,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sarkin Addar A</t>
+          <t>Yanfako</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2646,7 +2798,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Sabon Birni</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2655,13 +2807,13 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2679,12 +2831,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rijia B</t>
+          <t>Waziri A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2699,10 +2851,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2720,12 +2872,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tudun Wada B</t>
+          <t>Sarkin Adar Gidan Igwai</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2751,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2769,30 +2921,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sarkin Zamfara B</t>
+          <t>Arkilla</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dange-Shuni; Sokoto South; Wamako</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2810,12 +2970,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arkilla</t>
+          <t>Dundaye</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2826,7 +2986,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wamako</t>
+          <t>Kware; Wamako</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2835,13 +2995,13 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2859,30 +3019,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rijia A</t>
+          <t>Gidan Bubu</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -2900,12 +3068,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sarkin Addar B</t>
+          <t>Gidan Rugga More</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2916,7 +3084,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kware; Sokoto South; Wamako</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2925,13 +3093,13 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -2949,12 +3117,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Magajin Rafi B</t>
+          <t>Kalambaina</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -2965,7 +3133,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Wamako</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2974,13 +3142,13 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -2998,12 +3166,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sarkin Zamfara A</t>
+          <t>Magajin Gari A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -3021,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3034,17 +3202,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
+          <t>Magajin Gari B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -3056,13 +3224,13 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3075,35 +3243,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kyambarawa</t>
+          <t>Magajin Rafi A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3116,17 +3292,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kagara</t>
+          <t>Magajin Rafi B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -3137,7 +3313,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talata Mafara</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3146,13 +3322,13 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3165,35 +3341,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Galadima Dan Galadima</t>
+          <t>Rijia A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3206,35 +3390,43 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kungurki</t>
+          <t>Sarkin Adar Gandu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sokoto South; Wamako</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3247,35 +3439,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gabake</t>
+          <t>Sarkin Addar A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3288,35 +3488,43 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yankaba</t>
+          <t>Sarkin Addar B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3329,35 +3537,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dan' Isa</t>
+          <t>Sarkin Musulmi A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Birnin Magaji</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -3365,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3378,35 +3578,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kurya</t>
+          <t>Sarkin Musulmi B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Shinkafi; Zurmi</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>1</v>
       </c>
@@ -3414,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -3427,35 +3619,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sakajiki</t>
+          <t>Sarkin Zamfara A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
@@ -3468,17 +3668,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Sarkin Zamfara B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3489,7 +3689,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bungudu; Gusau</t>
+          <t>Sokoto South; Wamako</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3498,13 +3698,13 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -3517,17 +3717,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kanwa</t>
+          <t>Tudun Wada A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -3538,7 +3738,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zurmi</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3547,7 +3747,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -3563,23 +3763,2057 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Waziri B</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Waziri C</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kware; Sokoto South</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="10" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Sarkin Addar A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Rijia B</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="10" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Arkilla</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dange-Shuni; Sokoto North; Wamako</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Gagi A</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dange-Shuni; Kware</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="10" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tudun Wada A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" s="10" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Gagi B</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dange-Shuni; Wamako</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" s="10" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Sarkin Zamfara B</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sokoto North; Wamako</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" s="10" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Durbawa</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Kware</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" s="10" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Gagi C</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" s="10" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Gidan Rugga More</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Kware; Sokoto North; Wamako</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" s="10" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Magajin Rafi A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" s="10" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Magajin Rafi B</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" s="10" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Rijia A</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" s="10" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Rikina</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Dange-Shuni; Kware</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" s="10" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sarkin Adar Gandu</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sokoto North; Wamako</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" s="10" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sarkin Addar B</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" s="10" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sarkin Zamfara A</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Sokoto North</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" s="10" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tudun Wada B</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" s="10" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tuntube-Tsefe</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Dange-Shuni; Wamako</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Waziri C</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Kware; Sokoto North</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" s="10" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Gabake</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Zurmi</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>4</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>19</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" s="10" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Kungurki</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Maradun</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>18</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" s="10" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Kyambarawa</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Bungudu</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>10</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" s="10" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Yankaba</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Maradun; Zurmi</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>9</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" s="10" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Kagara</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Bungudu; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>8</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" s="10" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sarkin Mafara-Sarkin Baura</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Zurmi</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>7</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" s="10" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Dan' Isa</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Bungudu</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>6</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" s="10" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kurya</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Bungudu; Maradun; Shinkafi; Zurmi</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>6</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" s="10" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sakajiki</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Maradun</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>6</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bela Rawaiya</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Bungudu; Gusau</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" s="10" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Galadima Dan Galadima</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Birnin Magaji</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>3</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" s="10" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Banga</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Birnin Magaji</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" s="10" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dauran Birnin Tsaba</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Zurmi</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" s="10" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Gidan Goga</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Maradun; Zurmi</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" s="10" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Gora</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Birnin Magaji</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" s="10" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gusami Hayi</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Gusau</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" s="10" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Kanwa</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Maradun; Zurmi</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" s="10" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Madomawa West</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Zurmi</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" s="10" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Nahuche</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" s="10" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Nasarawa Mailayi</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Birnin Magaji</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" s="10" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3595,7 +5829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3889,7 +6123,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Darna Sabon Gari</t>
+          <t>Gidan Hamma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3934,7 +6168,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rungumawa Gatti</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4339,7 +6573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Mamman Suka</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4384,7 +6618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Asara</t>
+          <t>Rungumawa Gatti</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4394,7 +6628,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_7</t>
+          <t>non_idp_NG034008_8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -4429,7 +6663,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rungumawa Gatti</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4439,7 +6673,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_8</t>
+          <t>non_idp_NG034008_9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4469,33 +6703,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Illela</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tozai</t>
+          <t>Magajin Gari B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_9</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>idp_NG034016_1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -4514,12 +6752,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Isa North</t>
+          <t>Waziri A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4529,7 +6767,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>idp_NG034009_1</t>
+          <t>idp_NG034016_14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4539,12 +6777,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -4563,12 +6801,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gebe B</t>
+          <t>Kalambaina</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4578,7 +6816,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_1</t>
+          <t>non_idp_NG034016_1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4608,12 +6846,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Isa South</t>
+          <t>Waziri A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4623,18 +6861,18 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_10</t>
+          <t>non_idp_NG034016_10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4653,12 +6891,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bargaja</t>
+          <t>Sarkin Adar Gidan Igwai</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4668,18 +6906,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_15</t>
+          <t>non_idp_NG034016_2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -4698,12 +6936,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bargaja</t>
+          <t>Sarkin Addar A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4713,18 +6951,18 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_16</t>
+          <t>non_idp_NG034016_7</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -4743,33 +6981,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bargaja</t>
+          <t>Tudun Wada A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_17</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>idp_NG034017_1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4788,33 +7030,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gebe A</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_2</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>idp_NG034017_10</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4833,25 +7079,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gebe A</t>
+          <t>Gagi C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_3</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>idp_NG034017_9</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>6</t>
@@ -4878,12 +7128,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yanfako</t>
+          <t>Sarkin Addar A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4893,7 +7143,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_4</t>
+          <t>non_idp_NG034017_1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -4923,12 +7173,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tidibale</t>
+          <t>Gagi B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4938,18 +7188,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_5</t>
+          <t>non_idp_NG034017_12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4968,12 +7218,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tidibale</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4983,18 +7233,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_6</t>
+          <t>non_idp_NG034017_15</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -5013,12 +7263,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tsabre</t>
+          <t>Rijia B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5028,18 +7278,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_7</t>
+          <t>non_idp_NG034017_2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -5053,30 +7303,34 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Katuru</t>
+          <t>Yankaba</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_8</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>idp_NG037008_1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>6</t>
@@ -5098,38 +7352,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turba</t>
+          <t>Kagara</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG034009_9</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>idp_NG037008_12</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5143,17 +7401,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Magajin Gari B</t>
+          <t>Kyambarawa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5163,22 +7421,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>idp_NG034016_1</t>
+          <t>idp_NG037008_16</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>In-camp</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5192,17 +7450,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Waziri A</t>
+          <t>Kungurki</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5212,7 +7470,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>idp_NG034016_14</t>
+          <t>idp_NG037008_17</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5222,12 +7480,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5241,17 +7499,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gandu</t>
+          <t>Sakajiki</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5261,7 +7519,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>idp_NG034016_9</t>
+          <t>idp_NG037008_2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5271,12 +7529,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5290,38 +7548,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kalambaina</t>
+          <t>Sarkin Mafara-Sarkin Baura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>idp_NG037008_3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5335,38 +7597,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Waziri A</t>
+          <t>Galadima Dan Galadima</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_10</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>idp_NG037008_7</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5380,38 +7646,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gidan Igwai</t>
+          <t>Kyambarawa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_2</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>idp_NG037008_9</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5425,17 +7695,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gandu</t>
+          <t>Kungurki</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5445,18 +7715,18 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_7</t>
+          <t>non_idp_NG037008_1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5470,42 +7740,38 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tudun Wada A</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>idp_NG034017_1</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_12</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5519,42 +7785,38 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gagi A</t>
+          <t>Sarkin Mafara-Sarkin Baura</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>idp_NG034017_10</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_13</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5568,34 +7830,30 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gagi C</t>
+          <t>Gabake</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>idp_NG034017_9</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_14</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>6</t>
@@ -5617,17 +7875,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sarkin Addar A</t>
+          <t>Gabake</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5637,7 +7895,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_1</t>
+          <t>non_idp_NG037008_15</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -5662,17 +7920,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Gagi B</t>
+          <t>Gabake</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5682,18 +7940,18 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_12</t>
+          <t>non_idp_NG037008_16</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5707,17 +7965,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gagi A</t>
+          <t>Dan' Isa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5727,18 +7985,18 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_15</t>
+          <t>non_idp_NG037008_17</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5752,17 +8010,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kaura Namoda</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gagi C</t>
+          <t>Kurya</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5772,18 +8030,18 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_2</t>
+          <t>non_idp_NG037008_2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5812,19 +8070,15 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>idp_NG037008_1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_3</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>6</t>
@@ -5856,32 +8110,28 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kagara</t>
+          <t>Kungurki</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>idp_NG037008_12</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_4</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5905,24 +8155,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kyambarawa</t>
+          <t>Yankaba</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>idp_NG037008_16</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_6</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>6</t>
@@ -5954,24 +8200,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kungurki</t>
+          <t>Galadima Dan Galadima</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>idp_NG037008_17</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_7</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>6</t>
@@ -6003,24 +8245,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sakajiki</t>
+          <t>Kyambarawa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>idp_NG037008_2</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_8</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>6</t>
@@ -6057,27 +8295,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>idp_NG037008_3</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037008_9</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6088,751 +8322,23 @@
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Galadima Dan Galadima</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>IDP</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>idp_NG037008_7</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Kyambarawa</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>IDP</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>idp_NG037008_9</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Kungurki</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_1</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Bela Rawaiya</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_12</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_13</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Gabake</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_14</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Gabake</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_15</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Gabake</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_16</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Dan' Isa</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_17</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Kurya</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_2</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Yankaba</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_3</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_4</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Yankaba</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_6</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Galadima Dan Galadima</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_7</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Kyambarawa</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_8</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>non_idp_NG037008_9</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="M2:M53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7098,13 +8604,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67828DB2-7604-460A-9528-23C172D0A31F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33EC93B3-F53B-4C59-AFE0-F8B7FC3E01BB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41419B96-ED26-4507-924F-AD2F925C175B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93BFC9DD-A5A7-4088-B690-6A19DD967142}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D5EFD5A-4AF4-4C16-AD5C-FD0CCBA80729}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58CC15EB-26E4-42FB-BB7B-AA0F9A30D7A1}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/DRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/DRC_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O53" headerRowCount="1">
-  <autoFilter ref="A1:O53"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P77" headerRowCount="1">
+  <autoFilter ref="A1:P77"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 105 wards, 52 clusters</t>
+          <t>Assigned to you: 105 wards, 76 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -833,33 +844,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tozai</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Gada; Isa; Sabon Birni</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -882,25 +885,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Illela</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gada; Isa; Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -2836,25 +2847,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Waziri A</t>
+          <t>Kalambaina</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2877,7 +2896,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gidan Igwai</t>
+          <t>Sarkin Adar Gandu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2888,7 +2907,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wamako</t>
+          <t>Sokoto South; Wamako</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,13 +2916,13 @@
         </is>
       </c>
       <c r="H46" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" t="n">
         <v>1</v>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2926,33 +2945,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arkilla</t>
+          <t>Waziri B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Dange-Shuni; Sokoto South; Wamako</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2975,33 +2986,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dundaye</t>
+          <t>Waziri A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Kware; Wamako</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3024,33 +3027,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gidan Bubu</t>
+          <t>Magajin Gari B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Wamako</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3073,7 +3068,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gidan Rugga More</t>
+          <t>Sarkin Adar Gidan Igwai</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -3084,7 +3079,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kware; Sokoto South; Wamako</t>
+          <t>Wamako</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3093,13 +3088,13 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3122,25 +3117,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kalambaina</t>
+          <t>Magajin Gari A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Wamako</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -3148,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3171,25 +3158,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Magajin Gari A</t>
+          <t>Magajin Rafi A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
         <v>1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3212,25 +3207,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Magajin Gari B</t>
+          <t>Magajin Rafi B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
       <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3253,7 +3256,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Magajin Rafi A</t>
+          <t>Sarkin Zamfara A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -3279,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3302,7 +3305,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Magajin Rafi B</t>
+          <t>Waziri C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -3313,7 +3316,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kware; Sokoto South</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3328,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3351,7 +3354,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rijia A</t>
+          <t>Arkilla</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -3362,7 +3365,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Dange-Shuni; Sokoto South; Wamako</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3400,7 +3403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gandu</t>
+          <t>Dundaye</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -3411,7 +3414,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sokoto South; Wamako</t>
+          <t>Kware; Wamako</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3420,7 +3423,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -3449,7 +3452,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sarkin Addar A</t>
+          <t>Gidan Bubu</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -3460,7 +3463,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Wamako</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3469,7 +3472,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -3498,7 +3501,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sarkin Addar B</t>
+          <t>Gidan Rugga More</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -3509,7 +3512,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Kware; Sokoto South; Wamako</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3518,7 +3521,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -3547,19 +3550,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sarkin Musulmi A</t>
+          <t>Rijia A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -3588,19 +3599,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sarkin Musulmi B</t>
+          <t>Sarkin Addar A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sokoto South</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3629,7 +3648,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sarkin Zamfara A</t>
+          <t>Sarkin Addar B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -3649,7 +3668,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3678,27 +3697,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sarkin Zamfara B</t>
+          <t>Sarkin Musulmi A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Sokoto South; Wamako</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3727,27 +3738,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tudun Wada A</t>
+          <t>Sarkin Musulmi B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Sokoto South</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -3776,19 +3779,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Waziri B</t>
+          <t>Sarkin Zamfara B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sokoto South; Wamako</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -3817,7 +3828,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Waziri C</t>
+          <t>Tudun Wada A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -3828,7 +3839,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kware; Sokoto South</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3837,7 +3848,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -3866,7 +3877,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sarkin Addar A</t>
+          <t>Tudun Wada B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3877,7 +3888,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Wamako</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3886,13 +3897,13 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
@@ -3915,7 +3926,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rijia B</t>
+          <t>Gagi C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -3927,13 +3938,13 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
@@ -3956,7 +3967,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Arkilla</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -3967,7 +3978,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dange-Shuni; Sokoto North; Wamako</t>
+          <t>Dange-Shuni; Kware</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3976,13 +3987,13 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
@@ -4005,7 +4016,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gagi A</t>
+          <t>Tudun Wada A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -4016,7 +4027,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dange-Shuni; Kware</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4028,10 +4039,10 @@
         <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
@@ -4054,7 +4065,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tudun Wada A</t>
+          <t>Arkilla</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -4065,7 +4076,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Dange-Shuni; Sokoto North; Wamako</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4074,13 +4085,13 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -4103,7 +4114,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gagi B</t>
+          <t>Sarkin Addar A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -4114,7 +4125,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dange-Shuni; Wamako</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4123,13 +4134,13 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -4152,7 +4163,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sarkin Zamfara B</t>
+          <t>Gagi B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -4163,7 +4174,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sokoto North; Wamako</t>
+          <t>Dange-Shuni; Wamako</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4172,13 +4183,13 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
@@ -4201,7 +4212,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Durbawa</t>
+          <t>Waziri C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -4212,7 +4223,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kware</t>
+          <t>Kware; Sokoto North</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4221,13 +4232,13 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
@@ -4250,7 +4261,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gagi C</t>
+          <t>Rijia B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -4265,10 +4276,10 @@
         <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
@@ -4291,7 +4302,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gidan Rugga More</t>
+          <t>Sarkin Adar Gandu</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -4302,7 +4313,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kware; Sokoto North; Wamako</t>
+          <t>Sokoto North; Wamako</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4311,13 +4322,13 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -4340,7 +4351,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Magajin Rafi A</t>
+          <t>Sarkin Zamfara B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -4351,7 +4362,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Sokoto North; Wamako</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4360,13 +4371,13 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
@@ -4389,7 +4400,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Magajin Rafi B</t>
+          <t>Durbawa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -4400,7 +4411,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kware</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4409,7 +4420,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -4438,7 +4449,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rijia A</t>
+          <t>Gidan Rugga More</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -4449,7 +4460,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Kware; Sokoto North; Wamako</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4458,7 +4469,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -4487,7 +4498,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rikina</t>
+          <t>Magajin Rafi A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -4498,7 +4509,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dange-Shuni; Kware</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4536,7 +4547,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gandu</t>
+          <t>Magajin Rafi B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -4547,7 +4558,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sokoto North; Wamako</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4556,7 +4567,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -4585,7 +4596,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sarkin Addar B</t>
+          <t>Rijia A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -4634,7 +4645,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sarkin Zamfara A</t>
+          <t>Rikina</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -4645,7 +4656,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Dange-Shuni; Kware</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4654,7 +4665,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -4683,7 +4694,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tudun Wada B</t>
+          <t>Sarkin Addar B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -4694,7 +4705,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wamako</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4732,7 +4743,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tuntube-Tsefe</t>
+          <t>Sarkin Zamfara A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -4743,7 +4754,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dange-Shuni; Wamako</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4752,7 +4763,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -4781,7 +4792,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Waziri C</t>
+          <t>Tuntube-Tsefe</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -4792,7 +4803,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kware; Sokoto North</t>
+          <t>Dange-Shuni; Wamako</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4830,7 +4841,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gabake</t>
+          <t>Galadima Dan Galadima</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -4841,7 +4852,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Birnin Magaji; Zurmi</t>
+          <t>Birnin Magaji</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4853,10 +4864,10 @@
         <v>4</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
@@ -4879,7 +4890,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kungurki</t>
+          <t>Gabake</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -4890,7 +4901,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Maradun</t>
+          <t>Birnin Magaji; Zurmi</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4902,10 +4913,10 @@
         <v>4</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
@@ -4928,7 +4939,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kyambarawa</t>
+          <t>Kungurki</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -4939,7 +4950,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Birnin Magaji; Bungudu</t>
+          <t>Maradun</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4948,13 +4959,13 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -4977,7 +4988,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yankaba</t>
+          <t>Sarkin Mafara-Sarkin Baura</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -4988,7 +4999,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maradun; Zurmi</t>
+          <t>Zurmi</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4997,13 +5008,13 @@
         </is>
       </c>
       <c r="H90" t="n">
+        <v>5</v>
+      </c>
+      <c r="I90" t="n">
         <v>2</v>
       </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
       <c r="J90" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
@@ -5026,7 +5037,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kagara</t>
+          <t>Kyambarawa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5037,7 +5048,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Birnin Magaji; Bungudu; Talata Mafara</t>
+          <t>Birnin Magaji; Bungudu</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5046,13 +5057,13 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
@@ -5075,7 +5086,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
+          <t>Yankaba</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5086,7 +5097,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zurmi</t>
+          <t>Maradun; Zurmi</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5095,13 +5106,13 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
@@ -5124,7 +5135,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dan' Isa</t>
+          <t>Kagara</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -5135,7 +5146,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Birnin Magaji; Bungudu</t>
+          <t>Birnin Magaji; Bungudu; Talata Mafara</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5144,13 +5155,13 @@
         </is>
       </c>
       <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>1</v>
       </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
       <c r="J93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
@@ -5173,7 +5184,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kurya</t>
+          <t>Dan' Isa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -5184,7 +5195,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bungudu; Maradun; Shinkafi; Zurmi</t>
+          <t>Birnin Magaji; Bungudu</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5222,7 +5233,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sakajiki</t>
+          <t>Kurya</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -5233,7 +5244,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maradun</t>
+          <t>Bungudu; Maradun; Shinkafi; Zurmi</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5245,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>6</v>
@@ -5271,7 +5282,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Sakajiki</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -5282,7 +5293,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bungudu; Gusau</t>
+          <t>Maradun</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5291,13 +5302,13 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -5320,7 +5331,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Galadima Dan Galadima</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -5331,7 +5342,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Birnin Magaji</t>
+          <t>Bungudu; Gusau</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5340,13 +5351,13 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
@@ -5813,7 +5824,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5829,7 +5840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5837,16 +5848,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5877,50 +5889,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -5954,26 +5971,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5988,37 +6010,46 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kalmalo</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>idp_NG034008_supp1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6033,7 +6064,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Darna Sabon Gari</t>
+          <t>Kalmalo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6043,27 +6074,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_10</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>non_idp_NG034008_1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6078,7 +6114,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rungumawa Gatti</t>
+          <t>Darna Sabon Gari</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6088,27 +6124,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_11</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>non_idp_NG034008_10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6123,7 +6164,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gidan Hamma</t>
+          <t>Rungumawa Gatti</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6133,27 +6174,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_12</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>non_idp_NG034008_11</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6168,7 +6214,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tozai</t>
+          <t>Gidan Hamma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6178,27 +6224,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_13</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>non_idp_NG034008_12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6213,7 +6264,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gidan Hamma</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6223,27 +6274,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_14</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>non_idp_NG034008_13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6258,7 +6314,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kadadi</t>
+          <t>Gidan Hamma</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6268,27 +6324,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>non_idp_NG034008_14</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6303,7 +6364,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tozai</t>
+          <t>Kadadi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6313,27 +6374,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_16</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>non_idp_NG034008_15</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6348,7 +6414,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gidan Hamma</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6358,27 +6424,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_17</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>non_idp_NG034008_16</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6393,7 +6464,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kalmalo</t>
+          <t>Gidan Hamma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6403,27 +6474,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>non_idp_NG034008_17</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6438,7 +6514,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Illela</t>
+          <t>Kalmalo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6448,27 +6524,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>non_idp_NG034008_2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6483,7 +6564,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gidan Katta</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6493,27 +6574,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_4</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>non_idp_NG034008_3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6528,7 +6614,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Illela</t>
+          <t>Gidan Katta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6538,27 +6624,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_5</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>non_idp_NG034008_4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6573,7 +6664,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mamman Suka</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6583,27 +6674,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_6</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>non_idp_NG034008_5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6618,7 +6714,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rungumawa Gatti</t>
+          <t>Mamman Suka</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6628,27 +6724,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_8</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>non_idp_NG034008_6</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6663,7 +6764,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tozai</t>
+          <t>Rungumawa Gatti</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6673,27 +6774,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG034008_9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>non_idp_NG034008_8</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6703,46 +6809,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sokoto North</t>
+          <t>Illela</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Magajin Gari B</t>
+          <t>Tozai</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>idp_NG034016_1</t>
+          <t>non_idp_NG034008_9</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>In-camp</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6757,7 +6864,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waziri A</t>
+          <t>Magajin Gari B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6767,31 +6874,36 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>idp_NG034016_14</t>
+          <t>idp_NG034016_1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>In-host</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6806,37 +6918,46 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kalambaina</t>
+          <t>Waziri A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>idp_NG034016_14</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6851,37 +6972,46 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Waziri A</t>
+          <t>Sarkin Adar Gandu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_10</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>idp_NG034016_supp1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6896,37 +7026,46 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sarkin Adar Gidan Igwai</t>
+          <t>Kalambaina</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_2</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>idp_NG034016_supp2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6941,37 +7080,46 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sarkin Addar A</t>
+          <t>Waziri B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG034016_7</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>idp_NG034016_supp3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6981,46 +7129,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tudun Wada A</t>
+          <t>Kalambaina</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>idp_NG034017_1</t>
+          <t>non_idp_NG034016_1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7030,46 +7179,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gagi A</t>
+          <t>Waziri A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idp_NG034017_10</t>
+          <t>non_idp_NG034016_10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7079,46 +7229,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gagi C</t>
+          <t>Sarkin Adar Gidan Igwai</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG034017_9</t>
+          <t>non_idp_NG034016_2</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7128,7 +7279,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7143,27 +7294,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034016_7</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7173,12 +7329,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gagi B</t>
+          <t>Magajin Gari B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -7188,27 +7344,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_12</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG034016_supp1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7218,12 +7379,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gagi A</t>
+          <t>Kalambaina</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -7233,27 +7394,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_15</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG034016_supp2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7263,12 +7429,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sokoto South</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rijia B</t>
+          <t>Waziri A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -7278,91 +7444,97 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG034017_2</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>non_idp_NG034016_supp3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto North</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yankaba</t>
+          <t>Sarkin Adar Gandu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>idp_NG037008_1</t>
+          <t>non_idp_NG034016_supp4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kagara</t>
+          <t>Tudun Wada A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7372,46 +7544,51 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>idp_NG037008_12</t>
+          <t>idp_NG034017_1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kyambarawa</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7421,46 +7598,51 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>idp_NG037008_16</t>
+          <t>idp_NG034017_10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kungurki</t>
+          <t>Gagi C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7470,46 +7652,51 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>idp_NG037008_17</t>
+          <t>idp_NG034017_9</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sakajiki</t>
+          <t>Gagi C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7519,46 +7706,51 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>idp_NG037008_2</t>
+          <t>idp_NG034017_supp1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
+          <t>Gagi C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7568,46 +7760,51 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>idp_NG037008_3</t>
+          <t>idp_NG034017_supp2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Galadima Dan Galadima</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7617,46 +7814,51 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>idp_NG037008_7</t>
+          <t>idp_NG034017_supp3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kyambarawa</t>
+          <t>Tudun Wada B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7666,181 +7868,213 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>idp_NG037008_9</t>
+          <t>idp_NG034017_supp4</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kungurki</t>
+          <t>Tudun Wada B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_1</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>idp_NG034017_supp5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Tudun Wada B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_12</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>idp_NG034017_supp6</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
+          <t>Tudun Wada A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_13</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>idp_NG034017_supp7</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gabake</t>
+          <t>Sarkin Addar A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7850,42 +8084,47 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_14</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>non_idp_NG034017_1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gabake</t>
+          <t>Gagi B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7895,42 +8134,47 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_15</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034017_12</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Gabake</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7940,42 +8184,47 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_16</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034017_15</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dan' Isa</t>
+          <t>Rijia B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7985,42 +8234,47 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_17</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034017_2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kurya</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8030,42 +8284,47 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>non_idp_NG034017_supp1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yankaba</t>
+          <t>Tudun Wada A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8075,42 +8334,47 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_3</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>non_idp_NG034017_supp2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kungurki</t>
+          <t>Gagi A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8120,42 +8384,47 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_4</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG034017_supp3</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yankaba</t>
+          <t>Sarkin Addar A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8165,42 +8434,47 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_6</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>non_idp_NG034017_supp4</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Galadima Dan Galadima</t>
+          <t>Arkilla</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8210,42 +8484,47 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_7</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034017_supp5</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kaura Namoda</t>
+          <t>Sokoto South</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kyambarawa</t>
+          <t>Waziri C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8255,27 +8534,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_8</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034017_supp6</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8290,55 +8574,1304 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sarkin Mafara-Sarkin Baura</t>
+          <t>Yankaba</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG037008_9</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>idp_NG037008_1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Kagara</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>idp_NG037008_12</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Kyambarawa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>idp_NG037008_16</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Kungurki</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>idp_NG037008_17</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sakajiki</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>idp_NG037008_2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sarkin Mafara-Sarkin Baura</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>idp_NG037008_3</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Galadima Dan Galadima</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>idp_NG037008_7</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Kyambarawa</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>idp_NG037008_9</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sarkin Mafara-Sarkin Baura</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>idp_NG037008_supp1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Galadima Dan Galadima</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>idp_NG037008_supp2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Galadima Dan Galadima</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>idp_NG037008_supp3</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kungurki</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_1</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Bela Rawaiya</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_12</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sarkin Mafara-Sarkin Baura</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_13</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Gabake</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_14</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Gabake</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_15</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Gabake</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_16</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dan' Isa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_17</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Kurya</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_2</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Yankaba</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_3</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Kungurki</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_4</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Yankaba</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_6</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Galadima Dan Galadima</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_7</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Kyambarawa</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_8</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sarkin Mafara-Sarkin Baura</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>non_idp_NG037008_9</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8604,13 +10137,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33EC93B3-F53B-4C59-AFE0-F8B7FC3E01BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F77A1E4-E3BA-4961-BFB9-C475FD7AEB33}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93BFC9DD-A5A7-4088-B690-6A19DD967142}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FC5A72A-B37A-420E-A890-85D3DB3730BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58CC15EB-26E4-42FB-BB7B-AA0F9A30D7A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{806A19A6-57A6-486E-B11D-F91E3ABEE2EE}"/>
 </file>